--- a/data.xlsx
+++ b/data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
-  <workbookPr/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\kiosk\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AAED98AA-E72A-4493-A3F6-CEC394ACE73C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E81AC39-6578-4D55-9E5F-22291A04577C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2775" yWindow="4185" windowWidth="21600" windowHeight="11295" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" firstSheet="3" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="VERSION" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="37">
   <si>
     <t>id</t>
   </si>
@@ -127,6 +127,18 @@
   </si>
   <si>
     <t>Chicken Combo</t>
+  </si>
+  <si>
+    <t>French Fries Large</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>price</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>set_id</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -136,7 +148,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd\ h:mm:ss"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -151,6 +163,12 @@
       <family val="2"/>
       <charset val="129"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFCE9178"/>
+      <name val="Consolas"/>
+      <family val="3"/>
     </font>
   </fonts>
   <fills count="2">
@@ -175,12 +193,15 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -618,14 +639,15 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:J5"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
+    <col min="2" max="2" width="23.375" customWidth="1"/>
     <col min="6" max="6" width="14.625" style="1" customWidth="1"/>
     <col min="7" max="7" width="14.125" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -648,7 +670,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
@@ -665,55 +687,79 @@
         <v>23</v>
       </c>
       <c r="F2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G2">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C3">
+        <v>2300</v>
+      </c>
+      <c r="D3">
+        <v>450</v>
+      </c>
+      <c r="E3">
+        <v>0</v>
+      </c>
+      <c r="F3" t="b">
+        <v>1</v>
+      </c>
+      <c r="G3">
+        <v>300</v>
+      </c>
+      <c r="J3" s="3"/>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A4">
+        <v>2</v>
+      </c>
+      <c r="B4" t="s">
         <v>24</v>
-      </c>
-      <c r="C3">
-        <v>2200</v>
-      </c>
-      <c r="D3">
-        <v>340</v>
-      </c>
-      <c r="E3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F3" t="b">
-        <v>1</v>
-      </c>
-      <c r="G3">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A4">
-        <v>3</v>
-      </c>
-      <c r="B4" t="s">
-        <v>26</v>
       </c>
       <c r="C4">
         <v>2500</v>
       </c>
       <c r="D4">
+        <v>340</v>
+      </c>
+      <c r="E4" t="s">
+        <v>25</v>
+      </c>
+      <c r="F4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G4">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A5">
+        <v>3</v>
+      </c>
+      <c r="B5" t="s">
+        <v>26</v>
+      </c>
+      <c r="C5">
+        <v>2500</v>
+      </c>
+      <c r="D5">
         <v>120</v>
       </c>
-      <c r="E4" t="s">
+      <c r="E5" t="s">
         <v>27</v>
       </c>
-      <c r="F4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G4">
+      <c r="F5" t="b">
+        <v>0</v>
+      </c>
+      <c r="G5">
         <v>0</v>
       </c>
     </row>
@@ -818,6 +864,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:F4"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="23.5" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
@@ -907,13 +956,14 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="20.125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -935,8 +985,14 @@
       <c r="G1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H1" t="s">
+        <v>36</v>
+      </c>
+      <c r="I1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
@@ -958,8 +1014,14 @@
       <c r="G2">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H2">
+        <v>1</v>
+      </c>
+      <c r="I2">
+        <v>9000</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
@@ -980,6 +1042,12 @@
       </c>
       <c r="G3">
         <v>2</v>
+      </c>
+      <c r="H3">
+        <v>2</v>
+      </c>
+      <c r="I3">
+        <v>8600</v>
       </c>
     </row>
   </sheetData>

--- a/data.xlsx
+++ b/data.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\kiosk\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\program_practice\kiosk\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E81AC39-6578-4D55-9E5F-22291A04577C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9700D541-F98B-4529-8432-C3063257D5FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" firstSheet="3" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-14505" yWindow="0" windowWidth="14610" windowHeight="15585" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="VERSION" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="38">
   <si>
     <t>id</t>
   </si>
@@ -49,9 +49,6 @@
   </si>
   <si>
     <t>version_code</t>
-  </si>
-  <si>
-    <t>26.04.09.01</t>
   </si>
   <si>
     <t>menu_name</t>
@@ -138,6 +135,14 @@
   </si>
   <si>
     <t>set_id</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>26.04.09.01</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>is_upgradable</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -538,6 +543,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:A2"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="12.125" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
@@ -546,7 +554,7 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>8</v>
+        <v>36</v>
       </c>
     </row>
   </sheetData>
@@ -557,35 +565,39 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="17.375" style="1" customWidth="1"/>
+    <col min="5" max="5" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1" t="s">
         <v>9</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>10</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
+        <v>37</v>
+      </c>
+      <c r="F1" t="s">
         <v>11</v>
       </c>
-      <c r="E1" t="s">
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
         <v>12</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2">
-        <v>1</v>
-      </c>
-      <c r="B2" t="s">
-        <v>13</v>
       </c>
       <c r="C2">
         <v>5500</v>
@@ -593,16 +605,19 @@
       <c r="D2">
         <v>650</v>
       </c>
-      <c r="E2" t="s">
+      <c r="E2" t="b">
+        <v>1</v>
+      </c>
+      <c r="F2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
         <v>14</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A3">
-        <v>2</v>
-      </c>
-      <c r="B3" t="s">
-        <v>15</v>
       </c>
       <c r="C3">
         <v>4800</v>
@@ -610,16 +625,19 @@
       <c r="D3">
         <v>620</v>
       </c>
-      <c r="E3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C4">
         <v>5200</v>
@@ -627,8 +645,11 @@
       <c r="D4">
         <v>680</v>
       </c>
-      <c r="E4" t="s">
-        <v>18</v>
+      <c r="E4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F4" t="s">
+        <v>17</v>
       </c>
     </row>
   </sheetData>
@@ -652,22 +673,22 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1" t="s">
         <v>9</v>
       </c>
-      <c r="C1" t="s">
-        <v>10</v>
-      </c>
       <c r="D1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F1" t="s">
         <v>19</v>
       </c>
-      <c r="E1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>20</v>
-      </c>
-      <c r="G1" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
@@ -675,7 +696,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C2">
         <v>2000</v>
@@ -684,7 +705,7 @@
         <v>320</v>
       </c>
       <c r="E2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F2" t="b">
         <v>0</v>
@@ -698,7 +719,7 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C3">
         <v>2300</v>
@@ -722,7 +743,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C4">
         <v>2500</v>
@@ -731,7 +752,7 @@
         <v>340</v>
       </c>
       <c r="E4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F4" t="b">
         <v>1</v>
@@ -745,7 +766,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C5">
         <v>2500</v>
@@ -754,7 +775,7 @@
         <v>120</v>
       </c>
       <c r="E5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F5" t="b">
         <v>0</v>
@@ -779,19 +800,19 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1" t="s">
         <v>9</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>10</v>
       </c>
-      <c r="D1" t="s">
-        <v>11</v>
-      </c>
       <c r="E1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F1" t="s">
         <v>20</v>
-      </c>
-      <c r="F1" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
@@ -799,7 +820,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C2">
         <v>1500</v>
@@ -819,7 +840,7 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C3">
         <v>1500</v>
@@ -839,7 +860,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C4">
         <v>1800</v>
@@ -873,7 +894,7 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C1" t="s">
         <v>4</v>
@@ -885,7 +906,7 @@
         <v>6</v>
       </c>
       <c r="F1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
@@ -893,7 +914,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C2">
         <v>1</v>
@@ -913,7 +934,7 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C3">
         <v>2</v>
@@ -933,7 +954,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C4">
         <v>3</v>
@@ -986,10 +1007,10 @@
         <v>6</v>
       </c>
       <c r="H1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="I1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\program_practice\kiosk\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9700D541-F98B-4529-8432-C3063257D5FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A2628A5-418B-440F-9107-ABFF90E681A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-14505" yWindow="0" windowWidth="14610" windowHeight="15585" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="VERSION" sheetId="1" r:id="rId1"/>
@@ -33,9 +33,6 @@
     <t>date</t>
   </si>
   <si>
-    <t>order_number</t>
-  </si>
-  <si>
     <t>is_takeout</t>
   </si>
   <si>
@@ -57,9 +54,6 @@
     <t>price</t>
   </si>
   <si>
-    <t>kcal</t>
-  </si>
-  <si>
     <t>allergic</t>
   </si>
   <si>
@@ -79,9 +73,6 @@
   </si>
   <si>
     <t>10000001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">kcal </t>
   </si>
   <si>
     <t>is_upgradeable</t>
@@ -134,15 +125,27 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>set_id</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>26.04.09.01</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>is_upgradable</t>
+    <t>is_upgradeable</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>kcal</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>side_menu_id</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>order_number</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>set_menu_id</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -549,12 +552,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
     </row>
   </sheetData>
@@ -569,7 +572,8 @@
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="17.375" style="1" customWidth="1"/>
-    <col min="5" max="5" width="13" customWidth="1"/>
+    <col min="5" max="5" width="15.75" customWidth="1"/>
+    <col min="6" max="6" width="15.25" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
@@ -577,19 +581,19 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1" t="s">
         <v>8</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E1" t="s">
+        <v>33</v>
+      </c>
+      <c r="F1" t="s">
         <v>9</v>
-      </c>
-      <c r="D1" t="s">
-        <v>10</v>
-      </c>
-      <c r="E1" t="s">
-        <v>37</v>
-      </c>
-      <c r="F1" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
@@ -597,7 +601,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C2">
         <v>5500</v>
@@ -609,7 +613,7 @@
         <v>1</v>
       </c>
       <c r="F2" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
@@ -617,7 +621,7 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C3">
         <v>4800</v>
@@ -629,7 +633,7 @@
         <v>1</v>
       </c>
       <c r="F3" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
@@ -637,7 +641,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C4">
         <v>5200</v>
@@ -649,7 +653,7 @@
         <v>1</v>
       </c>
       <c r="F4" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
   </sheetData>
@@ -673,22 +677,22 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1" t="s">
         <v>8</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E1" t="s">
         <v>9</v>
       </c>
-      <c r="D1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E1" t="s">
-        <v>11</v>
-      </c>
       <c r="F1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="G1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
@@ -696,7 +700,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="C2">
         <v>2000</v>
@@ -705,7 +709,7 @@
         <v>320</v>
       </c>
       <c r="E2" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="F2" t="b">
         <v>0</v>
@@ -719,7 +723,7 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="C3">
         <v>2300</v>
@@ -740,10 +744,10 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="C4">
         <v>2500</v>
@@ -752,7 +756,7 @@
         <v>340</v>
       </c>
       <c r="E4" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F4" t="b">
         <v>1</v>
@@ -763,10 +767,10 @@
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="C5">
         <v>2500</v>
@@ -775,7 +779,7 @@
         <v>120</v>
       </c>
       <c r="E5" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="F5" t="b">
         <v>0</v>
@@ -794,25 +798,29 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:F4"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="4" max="4" width="12.75" customWidth="1"/>
+    <col min="5" max="5" width="14.375" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1" t="s">
         <v>8</v>
       </c>
-      <c r="C1" t="s">
-        <v>9</v>
-      </c>
       <c r="D1" t="s">
-        <v>10</v>
+        <v>34</v>
       </c>
       <c r="E1" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="F1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
@@ -820,7 +828,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="C2">
         <v>1500</v>
@@ -840,7 +848,7 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="C3">
         <v>1500</v>
@@ -860,13 +868,13 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C4">
         <v>1800</v>
       </c>
       <c r="D4">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E4" t="b">
         <v>1</v>
@@ -887,6 +895,7 @@
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="23.5" customWidth="1"/>
+    <col min="4" max="4" width="26.25" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
@@ -894,19 +903,19 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F1" t="s">
         <v>8</v>
-      </c>
-      <c r="C1" t="s">
-        <v>4</v>
-      </c>
-      <c r="D1" t="s">
-        <v>5</v>
-      </c>
-      <c r="E1" t="s">
-        <v>6</v>
-      </c>
-      <c r="F1" t="s">
-        <v>9</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
@@ -914,7 +923,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="C2">
         <v>1</v>
@@ -934,7 +943,7 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="C3">
         <v>2</v>
@@ -954,7 +963,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C4">
         <v>3</v>
@@ -982,6 +991,7 @@
   <cols>
     <col min="2" max="2" width="20.125" style="1" customWidth="1"/>
     <col min="3" max="3" width="18" customWidth="1"/>
+    <col min="8" max="8" width="18.5" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.3">
@@ -992,25 +1002,25 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>2</v>
+        <v>36</v>
       </c>
       <c r="D1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
-        <v>6</v>
-      </c>
       <c r="H1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="I1" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
